--- a/results/Int Task Remove ACC -0.6/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7082748284599595</v>
+        <v>0.7124345953033835</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7037668462379374</v>
+        <v>0.7104160013056318</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7039967035610826</v>
+        <v>0.7105496597337806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7013412974997433</v>
+        <v>0.7112562907394406</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7001323921904083</v>
+        <v>0.7093773346258339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.699184824281375</v>
+        <v>0.6933163399538809</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7025417612241424</v>
+        <v>0.69489561980227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7169749369343259</v>
+        <v>0.6873899955963065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7115841056211107</v>
+        <v>0.6958491671672995</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7236172332142601</v>
+        <v>0.6978192220516709</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7131616268059715</v>
+        <v>0.6655558361600918</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7165560232818913</v>
+        <v>0.6829347732801325</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7165560232818913</v>
+        <v>0.6748987361540421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7118020040322637</v>
+        <v>0.6716490776864992</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7159294114667676</v>
+        <v>0.6716490776864992</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7159294114667676</v>
+        <v>0.6736191325708706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7078184552743727</v>
+        <v>0.672987420631515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7117423853386553</v>
+        <v>0.6449792970129451</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7138784580600956</v>
+        <v>0.6015698534118776</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7172941343647075</v>
+        <v>0.6015698534118776</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7196498641608291</v>
+        <v>0.6075336573026041</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7207634499069315</v>
+        <v>0.6089307396094641</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7228407832665276</v>
+        <v>0.608224108603804</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7215237201502039</v>
+        <v>0.6054988836003923</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7025127432759258</v>
+        <v>0.6153551374782453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7034441314804993</v>
+        <v>0.623090619007354</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.699595120482521</v>
+        <v>0.6233953953968038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6955800916474738</v>
+        <v>0.6233953953968038</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6827210956614475</v>
+        <v>0.6244706422779898</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6844502136424454</v>
+        <v>0.6170654377594909</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6755415276736259</v>
+        <v>0.6177082292790745</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6791708815969227</v>
+        <v>0.6177082292790745</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6810072780531453</v>
+        <v>0.619341148365076</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6810711175392217</v>
+        <v>0.6199515804757396</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6884805428501886</v>
+        <v>0.6105942594408575</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.689074795256392</v>
+        <v>0.6207450894596963</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6822221628184764</v>
+        <v>0.6221370716423245</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6822221628184764</v>
+        <v>0.6193845873542244</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6806539625503154</v>
+        <v>0.6193845873542244</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6831271710701257</v>
+        <v>0.6041494610751483</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6805032450859424</v>
+        <v>0.6097905502084369</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6805032450859424</v>
+        <v>0.6048900342869041</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6726281256726888</v>
+        <v>0.6015441769243648</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6805415839508587</v>
+        <v>0.5946190875490843</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6770246086270184</v>
+        <v>0.5781076991475406</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.647408187211843</v>
+        <v>0.5872624221439656</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6351467850927237</v>
+        <v>0.58698402570744</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6065945309785064</v>
+        <v>0.5861488363978632</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6376991334713064</v>
+        <v>0.5657995165785693</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6395729894606812</v>
+        <v>0.5398864888212311</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5958791699670919</v>
+        <v>0.5466854820215346</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.596773098638513</v>
+        <v>0.5468514998586035</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5942675307097826</v>
+        <v>0.5477241487013325</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5827459983370078</v>
+        <v>0.5450151034023808</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5869747047907402</v>
+        <v>0.5502671761632152</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5642891763404885</v>
+        <v>0.5506954107323497</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5629346536910127</v>
+        <v>0.5475955903974158</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.560573823770659</v>
+        <v>0.5411388331197143</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.560573823770659</v>
+        <v>0.5400252473736119</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.55936403912956</v>
+        <v>0.5396719318707819</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5624366001798058</v>
+        <v>0.5358118412925754</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5590371035796541</v>
+        <v>0.5342964009302626</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5560547619684088</v>
+        <v>0.5257784899974253</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5591647825518067</v>
+        <v>0.511226956231789</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5585705301456032</v>
+        <v>0.509331820413722</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5577940801978707</v>
+        <v>0.5093692799468743</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5449614641647684</v>
+        <v>0.5233802005439194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5449614641647684</v>
+        <v>0.5200070838966919</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5514556809756221</v>
+        <v>0.5214365256124721</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5039691277169593</v>
+        <v>0.5231069042316259</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4975276708119539</v>
+        <v>0.5183903445151505</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5041981057083404</v>
+        <v>0.5183903445151505</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5016712579509178</v>
+        <v>0.513116991925624</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5019019946058272</v>
+        <v>0.5102742881985236</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5124265406244241</v>
+        <v>0.5106863430631979</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5133366490003053</v>
+        <v>0.5110234788615678</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5028001440697162</v>
+        <v>0.5018738559893748</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5038762702826665</v>
+        <v>0.5018738559893748</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5033943964759197</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5039886488821231</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5072919465872783</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5052146132276822</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5057714061007335</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5057714061007335</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5073668656535827</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5005576722048154</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4972543744996602</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4951132016539879</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4959322112591046</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
